--- a/docs/downloads/05/tbl_agri_equip_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_tous.xlsx
@@ -436,12 +436,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +448,6 @@
           <t>Couteau</t>
         </is>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -508,12 +496,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -526,12 +508,6 @@
           <t>Nasse</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -544,12 +520,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -562,12 +532,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -580,12 +544,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -616,12 +574,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +586,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -701,12 +647,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -719,12 +659,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -737,12 +671,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -755,12 +683,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -773,12 +695,6 @@
           <t>Charrue</t>
         </is>
       </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -845,12 +761,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -863,12 +773,6 @@
           <t>Herse/Pulvériseur/Rotovat</t>
         </is>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -881,12 +785,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -899,12 +797,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -935,12 +827,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -971,12 +857,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -989,12 +869,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1007,12 +881,6 @@
           <t>Soubique, produits de tis</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1025,12 +893,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1092,12 +954,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1110,12 +966,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1128,12 +978,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-      <c r="D44">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1146,12 +990,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1164,12 +1002,6 @@
           <t>Charrue</t>
         </is>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1200,12 +1032,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1254,12 +1080,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C51">
-        <v>4</v>
-      </c>
-      <c r="D51">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1272,12 +1092,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1290,12 +1104,6 @@
           <t>Pioche</t>
         </is>
       </c>
-      <c r="C53">
-        <v>2</v>
-      </c>
-      <c r="D53">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1308,12 +1116,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C54">
-        <v>3</v>
-      </c>
-      <c r="D54">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1326,12 +1128,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1380,12 +1176,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1447,12 +1237,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1465,12 +1249,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1483,12 +1261,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-      <c r="D64">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1501,12 +1273,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1519,12 +1285,6 @@
           <t>Charrue</t>
         </is>
       </c>
-      <c r="C66">
-        <v>3</v>
-      </c>
-      <c r="D66">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1537,12 +1297,6 @@
           <t>Couteau</t>
         </is>
       </c>
-      <c r="C67">
-        <v>4</v>
-      </c>
-      <c r="D67">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1609,12 +1363,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C71">
-        <v>3</v>
-      </c>
-      <c r="D71">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1627,12 +1375,6 @@
           <t>Nasse</t>
         </is>
       </c>
-      <c r="C72">
-        <v>4</v>
-      </c>
-      <c r="D72">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1645,12 +1387,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C73">
-        <v>2</v>
-      </c>
-      <c r="D73">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1663,12 +1399,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C74">
-        <v>3</v>
-      </c>
-      <c r="D74">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1699,12 +1429,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C76">
-        <v>3</v>
-      </c>
-      <c r="D76">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1717,12 +1441,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1784,12 +1502,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1802,12 +1514,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1820,12 +1526,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C83">
-        <v>2</v>
-      </c>
-      <c r="D83">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1838,12 +1538,6 @@
           <t>Charrue</t>
         </is>
       </c>
-      <c r="C84">
-        <v>3</v>
-      </c>
-      <c r="D84">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1910,12 +1604,6 @@
           <t>Herse/Pulvériseur/Rotovat</t>
         </is>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1928,12 +1616,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C89">
-        <v>2</v>
-      </c>
-      <c r="D89">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1946,12 +1628,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C90">
-        <v>2</v>
-      </c>
-      <c r="D90">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1964,12 +1640,6 @@
           <t>Pioche</t>
         </is>
       </c>
-      <c r="C91">
-        <v>4</v>
-      </c>
-      <c r="D91">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1982,12 +1652,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2000,12 +1664,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C93">
-        <v>2</v>
-      </c>
-      <c r="D93">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2036,12 +1694,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2103,12 +1755,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2121,12 +1767,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2139,12 +1779,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C101">
-        <v>3</v>
-      </c>
-      <c r="D101">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2157,12 +1791,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C102">
-        <v>3</v>
-      </c>
-      <c r="D102">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2175,12 +1803,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2193,12 +1815,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C104">
-        <v>1</v>
-      </c>
-      <c r="D104">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2283,12 +1899,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C109">
-        <v>4</v>
-      </c>
-      <c r="D109">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2319,12 +1929,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C111">
-        <v>2</v>
-      </c>
-      <c r="D111">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2337,12 +1941,6 @@
           <t>Nasse</t>
         </is>
       </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2409,12 +2007,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C116">
-        <v>2</v>
-      </c>
-      <c r="D116">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2427,12 +2019,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C117">
-        <v>3</v>
-      </c>
-      <c r="D117">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2445,12 +2031,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C118">
-        <v>1</v>
-      </c>
-      <c r="D118">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2463,12 +2043,6 @@
           <t>Soubique, produits de tis</t>
         </is>
       </c>
-      <c r="C119">
-        <v>1</v>
-      </c>
-      <c r="D119">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2481,12 +2055,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C120">
-        <v>3</v>
-      </c>
-      <c r="D120">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2548,12 +2116,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C124">
-        <v>1</v>
-      </c>
-      <c r="D124">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2584,12 +2146,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C126">
-        <v>1</v>
-      </c>
-      <c r="D126">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2674,12 +2230,6 @@
           <t>Herse/Pulvériseur/Rotovat</t>
         </is>
       </c>
-      <c r="C131">
-        <v>4</v>
-      </c>
-      <c r="D131">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2692,12 +2242,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C132">
-        <v>2</v>
-      </c>
-      <c r="D132">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2710,12 +2254,6 @@
           <t>Pioche</t>
         </is>
       </c>
-      <c r="C133">
-        <v>2</v>
-      </c>
-      <c r="D133">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2782,12 +2320,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C137">
-        <v>2</v>
-      </c>
-      <c r="D137">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2849,12 +2381,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C141">
-        <v>1</v>
-      </c>
-      <c r="D141">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2867,12 +2393,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C142">
-        <v>1</v>
-      </c>
-      <c r="D142">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2885,12 +2405,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C143">
-        <v>4</v>
-      </c>
-      <c r="D143">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2939,12 +2453,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C146">
-        <v>2</v>
-      </c>
-      <c r="D146">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2993,12 +2501,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C149">
-        <v>3</v>
-      </c>
-      <c r="D149">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3011,12 +2513,6 @@
           <t>Herse/Pulvériseur/Rotovat</t>
         </is>
       </c>
-      <c r="C150">
-        <v>4</v>
-      </c>
-      <c r="D150">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3029,12 +2525,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C151">
-        <v>3</v>
-      </c>
-      <c r="D151">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3047,12 +2537,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C152">
-        <v>2</v>
-      </c>
-      <c r="D152">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3137,12 +2621,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C157">
-        <v>1</v>
-      </c>
-      <c r="D157">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3204,12 +2682,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C161">
-        <v>3</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3222,12 +2694,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C162">
-        <v>3</v>
-      </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3240,12 +2706,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C163">
-        <v>4</v>
-      </c>
-      <c r="D163">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3276,12 +2736,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C165">
-        <v>2</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3312,12 +2766,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C167">
-        <v>1</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3330,12 +2778,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C168">
-        <v>3</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3348,12 +2790,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3402,12 +2838,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C172">
-        <v>3</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3600,12 +3030,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C183">
-        <v>1</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3654,12 +3078,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C186">
-        <v>4</v>
-      </c>
-      <c r="D186">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3672,12 +3090,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C187">
-        <v>3</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3689,12 +3101,6 @@
         <is>
           <t>Soubique, produits de tis</t>
         </is>
-      </c>
-      <c r="C188">
-        <v>2</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
       </c>
     </row>
     <row r="189">

--- a/docs/downloads/05/tbl_agri_equip_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1513,7 +1513,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1645,7 +1645,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1747,7 +1747,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1867,7 +1867,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1933,7 +1933,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1969,7 +1969,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2035,7 +2035,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2107,7 +2107,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2143,7 +2143,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
